--- a/data/videos_entropy_fm.xlsx
+++ b/data/videos_entropy_fm.xlsx
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11 15:32</t>
+          <t>2026-08-17 10:00</t>
         </is>
       </c>
     </row>
